--- a/part1/Estimate CPU Performance.xlsx
+++ b/part1/Estimate CPU Performance.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11108"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ost/Dropbox/Loughborough/teaching/modules/2020-21/WSD530:WSP030/courseworks/cw1/quiz/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucas\Documents\openMP\openMP\part1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{825B788E-2425-5641-B263-E4F57C4DFA4E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DD24E4-3DCC-4D85-9878-6EB7FFC18374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20910" windowHeight="13740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="5x5" sheetId="7" r:id="rId1"/>
+    <sheet name="10x10" sheetId="6" r:id="rId2"/>
+    <sheet name="50x50" sheetId="5" r:id="rId3"/>
+    <sheet name="100x100" sheetId="8" r:id="rId4"/>
+    <sheet name="1000x1000" sheetId="4" r:id="rId5"/>
+    <sheet name="1500x1500" sheetId="1" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="23">
   <si>
     <t># of CPU Cores</t>
   </si>
@@ -106,7 +111,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -151,6 +156,31 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -198,25 +228,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -235,7 +268,1747 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="1600" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1600" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Parallelization Efficiency</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'5x5'!$C$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Calculated Speedup</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'5x5'!$C$11:$C$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.1576354679802959E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0141987829614606E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.9665871121718375E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.7907505686125857E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.6123301985370951E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.1114864864864866E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.8773701798520634E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3419-47C8-8AF0-3973C2FE4F4B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'5x5'!$D$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Amdahl's Law Speedup</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'5x5'!$D$11:$D$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3419-47C8-8AF0-3973C2FE4F4B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="594020790"/>
+        <c:axId val="139199145"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="594020790"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:rPr>
+                  <a:t># of CPU Cores</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="139199145"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="139199145"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:rPr>
+                  <a:t>Speedup</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="594020790"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Roboto"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="1600" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1600" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Parallelization Efficiency</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10x10'!$C$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Calculated Speedup</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'10x10'!$C$11:$C$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.39506172839506171</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.31372549019607848</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.14953271028037385</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.17937219730941703</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.14773776546629733</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.8317677198975232E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.2429063908777515E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-02D5-4A9F-83EE-232C41A9E389}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10x10'!$D$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Amdahl's Law Speedup</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'10x10'!$D$11:$D$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-02D5-4A9F-83EE-232C41A9E389}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="594020790"/>
+        <c:axId val="139199145"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="594020790"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:rPr>
+                  <a:t># of CPU Cores</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="139199145"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="139199145"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:rPr>
+                  <a:t>Speedup</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="594020790"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Roboto"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="1600" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1600" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Parallelization Efficiency</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'50x50'!$C$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Calculated Speedup</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'50x50'!$C$11:$C$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.518854415274463</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5613346418056917</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7135164243403338</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.839306358381503</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.8940476190476188</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6791556728232189</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.83648790746582535</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-31B2-44FB-A565-EACE0FC40481}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'50x50'!$D$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Amdahl's Law Speedup</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'50x50'!$D$11:$D$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3986013986013985</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.6129032258064517</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7467248908296944</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.838235294117647</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.9047619047619047</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.9553072625698322</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.9950124688279298</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-31B2-44FB-A565-EACE0FC40481}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="594020790"/>
+        <c:axId val="139199145"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="594020790"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:rPr>
+                  <a:t># of CPU Cores</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="139199145"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="139199145"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:rPr>
+                  <a:t>Speedup</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="594020790"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Roboto"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="1600" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1600" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Parallelization Efficiency</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'100x100'!$C$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Calculated Speedup</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'100x100'!$C$11:$C$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3030620467365026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.0855042558679391</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.1521160500399255</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.149541406353848</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.887151359551873</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.2461277645064344</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.2999573318162425</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-08C8-4BDD-B39B-059D3A87B1EC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'100x100'!$D$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Amdahl's Law Speedup</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'100x100'!$D$11:$D$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5384615384615383</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.875</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.1052631578947367</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.2727272727272725</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.5806451612903221</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-08C8-4BDD-B39B-059D3A87B1EC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="594020790"/>
+        <c:axId val="139199145"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="594020790"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:rPr>
+                  <a:t># of CPU Cores</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="139199145"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="139199145"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:rPr>
+                  <a:t>Speedup</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="594020790"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Roboto"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="1600" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1600" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Parallelization Efficiency</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'1000x1000'!$C$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Calculated Speedup</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'1000x1000'!$C$11:$C$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.465691440776808</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.1563349562233176</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.6934975725648176</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.8955360612958745</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.9317124587168855</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.992526072673543</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.0665177062048889</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9435-4E01-84DD-5C7BDC3A44D3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'1000x1000'!$D$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Amdahl's Law Speedup</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'1000x1000'!$D$11:$D$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.6949152542372878</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.2058823529411762</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.5974025974025974</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.9069767441860463</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.1578947368421049</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.3653846153846154</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.5398230088495573</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9435-4E01-84DD-5C7BDC3A44D3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="594020790"/>
+        <c:axId val="139199145"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="594020790"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:rPr>
+                  <a:t># of CPU Cores</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="139199145"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="139199145"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:rPr>
+                  <a:t>Speedup</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="594020790"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Roboto"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -278,7 +2051,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$10</c:f>
+              <c:f>'1500x1500'!$C$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -292,7 +2065,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$11:$C$30</c:f>
+              <c:f>'1500x1500'!$C$11:$C$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -300,31 +2073,25 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9658848614072493</c:v>
+                  <c:v>1.6328365567407446</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.8060869565217392</c:v>
+                  <c:v>2.2851061839274021</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.7523255813953487</c:v>
+                  <c:v>2.8845005554099887</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.6001425516749812</c:v>
+                  <c:v>2.9489490622488672</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.4927659574468084</c:v>
+                  <c:v>3.1705472895133942</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.9759259259259254</c:v>
+                  <c:v>3.2722903470248137</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.5991820040899798</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>7.1314917127071817</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>7.5662368112543961</c:v>
+                  <c:v>3.2066823660695976</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -341,7 +2108,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$D$10</c:f>
+              <c:f>'1500x1500'!$D$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -355,7 +2122,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$11:$D$30</c:f>
+              <c:f>'1500x1500'!$D$11:$D$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -363,31 +2130,25 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.941747572815534</c:v>
+                  <c:v>1.7391304347826089</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.8301886792452828</c:v>
+                  <c:v>2.3076923076923075</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.6697247706422016</c:v>
+                  <c:v>2.7586206896551722</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.4642857142857135</c:v>
+                  <c:v>3.125</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.2173913043478262</c:v>
+                  <c:v>3.4285714285714284</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.9322033898305078</c:v>
+                  <c:v>3.6842105263157889</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.6115702479338836</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>7.2580645161290311</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>7.8740157480314945</c:v>
+                  <c:v>3.9024390243902434</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -590,6 +2351,196 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6315075" cy="3124200"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F61913AC-BD16-46E4-A558-3BF4B33B8BCE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6667500" cy="3533775"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D60F60C-92A4-4146-9319-D1CA61E31A04}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6667500" cy="3533775"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5795F415-1DAB-4FFF-BE70-000626C6A6A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6667500" cy="3533775"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{855522B0-B1FF-4F55-AD61-47659D507562}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6667500" cy="3533775"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C81D0064-AC18-4068-9BE1-0500385EBDF2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>476250</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
@@ -622,7 +2573,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -917,20 +2868,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90CD8DF2-EE33-4481-9AD9-EA04A1FE1BF0}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:G38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.1640625" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="5" max="5" width="19.1640625" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -938,7 +2889,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -946,7 +2897,7 @@
       <c r="F2" s="2"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>18</v>
       </c>
@@ -956,7 +2907,7 @@
       <c r="F3" s="2"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
@@ -966,8 +2917,8 @@
       <c r="F4" s="2"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B5" s="2"/>
@@ -976,8 +2927,8 @@
       <c r="F5" s="2"/>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="2"/>
@@ -986,7 +2937,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
@@ -996,15 +2947,15 @@
       <c r="F7" s="2"/>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="13"/>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="3"/>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1012,7 +2963,7 @@
       <c r="F9" s="2"/>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>0</v>
       </c>
@@ -1030,251 +2981,231 @@
       </c>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>1</v>
       </c>
-      <c r="B11" s="7">
-        <v>645.4</v>
-      </c>
-      <c r="C11" s="8">
-        <f t="shared" ref="C11:C20" si="0">B$11/B11</f>
+      <c r="B11" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="C11" s="7">
+        <f t="shared" ref="C11:C18" si="0">B$11/B11</f>
         <v>1</v>
       </c>
-      <c r="D11" s="8">
-        <f t="shared" ref="D11:D20" si="1">1/((1-F$11)+F$11/$A11)</f>
+      <c r="D11" s="7">
+        <f t="shared" ref="D11:D18" si="1">1/((1-F$11)+F$11/$A11)</f>
         <v>1</v>
       </c>
-      <c r="F11" s="9">
-        <v>0.97</v>
+      <c r="F11" s="8">
+        <v>0</v>
       </c>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>2</v>
       </c>
-      <c r="B12" s="7">
-        <v>328.3</v>
-      </c>
-      <c r="C12" s="8">
+      <c r="B12" s="6">
+        <v>8.1199999999999994E-2</v>
+      </c>
+      <c r="C12" s="7">
         <f t="shared" si="0"/>
-        <v>1.9658848614072493</v>
-      </c>
-      <c r="D12" s="8">
+        <v>6.1576354679802959E-3</v>
+      </c>
+      <c r="D12" s="7">
         <f t="shared" si="1"/>
-        <v>1.941747572815534</v>
+        <v>1</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="10"/>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>3</v>
       </c>
-      <c r="B13" s="7">
-        <v>230</v>
-      </c>
-      <c r="C13" s="8">
+      <c r="B13" s="6">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="C13" s="7">
         <f t="shared" si="0"/>
-        <v>2.8060869565217392</v>
-      </c>
-      <c r="D13" s="8">
+        <v>1.0141987829614606E-2</v>
+      </c>
+      <c r="D13" s="7">
         <f t="shared" si="1"/>
-        <v>2.8301886792452828</v>
+        <v>1</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="10"/>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>4</v>
       </c>
-      <c r="B14" s="7">
-        <v>172</v>
-      </c>
-      <c r="C14" s="8">
+      <c r="B14" s="6">
+        <v>8.3799999999999999E-2</v>
+      </c>
+      <c r="C14" s="7">
         <f t="shared" si="0"/>
-        <v>3.7523255813953487</v>
-      </c>
-      <c r="D14" s="8">
+        <v>5.9665871121718375E-3</v>
+      </c>
+      <c r="D14" s="7">
         <f t="shared" si="1"/>
-        <v>3.6697247706422016</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>5</v>
       </c>
-      <c r="B15" s="7">
-        <v>140.30000000000001</v>
-      </c>
-      <c r="C15" s="8">
+      <c r="B15" s="6">
+        <v>0.13189999999999999</v>
+      </c>
+      <c r="C15" s="7">
         <f t="shared" si="0"/>
-        <v>4.6001425516749812</v>
-      </c>
-      <c r="D15" s="8">
+        <v>3.7907505686125857E-3</v>
+      </c>
+      <c r="D15" s="7">
         <f t="shared" si="1"/>
-        <v>4.4642857142857135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>6</v>
       </c>
-      <c r="B16" s="7">
-        <v>117.5</v>
-      </c>
-      <c r="C16" s="8">
+      <c r="B16" s="6">
+        <v>0.19139999999999999</v>
+      </c>
+      <c r="C16" s="7">
         <f t="shared" si="0"/>
-        <v>5.4927659574468084</v>
-      </c>
-      <c r="D16" s="8">
+        <v>2.6123301985370951E-3</v>
+      </c>
+      <c r="D16" s="7">
         <f t="shared" si="1"/>
-        <v>5.2173913043478262</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>7</v>
       </c>
-      <c r="B17" s="7">
-        <v>108</v>
-      </c>
-      <c r="C17" s="8">
+      <c r="B17" s="6">
+        <v>0.23680000000000001</v>
+      </c>
+      <c r="C17" s="7">
         <f t="shared" si="0"/>
-        <v>5.9759259259259254</v>
-      </c>
-      <c r="D17" s="8">
+        <v>2.1114864864864866E-3</v>
+      </c>
+      <c r="D17" s="7">
         <f t="shared" si="1"/>
-        <v>5.9322033898305078</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>8</v>
       </c>
-      <c r="B18" s="7">
-        <v>97.8</v>
-      </c>
-      <c r="C18" s="8">
+      <c r="B18" s="6">
+        <v>2.6633</v>
+      </c>
+      <c r="C18" s="7">
         <f t="shared" si="0"/>
-        <v>6.5991820040899798</v>
-      </c>
-      <c r="D18" s="8">
+        <v>1.8773701798520634E-4</v>
+      </c>
+      <c r="D18" s="7">
         <f t="shared" si="1"/>
-        <v>6.6115702479338836</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="2">
-        <v>9</v>
-      </c>
-      <c r="B19" s="7">
-        <v>90.5</v>
-      </c>
-      <c r="C19" s="8">
-        <f t="shared" si="0"/>
-        <v>7.1314917127071817</v>
-      </c>
-      <c r="D19" s="8">
-        <f t="shared" si="1"/>
-        <v>7.2580645161290311</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="2">
-        <v>10</v>
-      </c>
-      <c r="B20" s="7">
-        <v>85.3</v>
-      </c>
-      <c r="C20" s="8">
-        <f t="shared" si="0"/>
-        <v>7.5662368112543961</v>
-      </c>
-      <c r="D20" s="8">
-        <f t="shared" si="1"/>
-        <v>7.8740157480314945</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-    </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-    </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-    </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-    </row>
-    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-    </row>
-    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-    </row>
-    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-    </row>
-    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-    </row>
-    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-    </row>
-    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="7"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-    </row>
-    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-    </row>
-    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>7</v>
       </c>
@@ -1297,92 +3228,2297 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="12">
+        <v>8</v>
+      </c>
+      <c r="C34" s="12">
+        <v>2</v>
+      </c>
+      <c r="D34" s="7">
+        <f t="shared" ref="D34:D36" si="2">1/((1-$F$11)+$F$11/B34)</f>
+        <v>1</v>
+      </c>
+      <c r="E34" s="7">
+        <f t="shared" ref="E34:E36" si="3">D34*C34</f>
+        <v>2</v>
+      </c>
+      <c r="F34" s="9">
+        <f>ROUND(($E$34/E34)*MIN($B$11:$B$30),1)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="12">
+        <v>8</v>
+      </c>
+      <c r="C35" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="D35" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E35" s="7">
+        <f t="shared" si="3"/>
+        <v>3.2</v>
+      </c>
+      <c r="F35" s="9">
+        <f>ROUND(($E$34/E35)*MIN($B$11:$B$30),1)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" t="e">
+        <f t="shared" ref="G35:G36" si="4">ROUND(100*((F34-F35)/F34),2)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="12">
+        <v>12</v>
+      </c>
+      <c r="C36" s="12">
+        <v>2.6</v>
+      </c>
+      <c r="D36" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E36" s="7">
+        <f t="shared" si="3"/>
+        <v>2.6</v>
+      </c>
+      <c r="F36" s="9">
+        <f>ROUND(($E$34/E36)*MIN($B$11:$B$30),1)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C38" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C39188A-DF0D-4D98-A1E4-3B5057F39A8A}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>1</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1.6E-2</v>
+      </c>
+      <c r="C11" s="7">
+        <f t="shared" ref="C11:C18" si="0">B$11/B11</f>
+        <v>1</v>
+      </c>
+      <c r="D11" s="7">
+        <f t="shared" ref="D11:D18" si="1">1/((1-F$11)+F$11/$A11)</f>
+        <v>1</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>2</v>
+      </c>
+      <c r="B12" s="6">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="C12" s="7">
+        <f t="shared" si="0"/>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="D12" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>3</v>
+      </c>
+      <c r="B13" s="6">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="C13" s="7">
+        <f t="shared" si="0"/>
+        <v>0.31372549019607848</v>
+      </c>
+      <c r="D13" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>4</v>
+      </c>
+      <c r="B14" s="6">
+        <v>0.107</v>
+      </c>
+      <c r="C14" s="7">
+        <f t="shared" si="0"/>
+        <v>0.14953271028037385</v>
+      </c>
+      <c r="D14" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>5</v>
+      </c>
+      <c r="B15" s="6">
+        <v>8.9200000000000002E-2</v>
+      </c>
+      <c r="C15" s="7">
+        <f t="shared" si="0"/>
+        <v>0.17937219730941703</v>
+      </c>
+      <c r="D15" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>6</v>
+      </c>
+      <c r="B16" s="6">
+        <v>0.10829999999999999</v>
+      </c>
+      <c r="C16" s="7">
+        <f t="shared" si="0"/>
+        <v>0.14773776546629733</v>
+      </c>
+      <c r="D16" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>7</v>
+      </c>
+      <c r="B17" s="6">
+        <v>0.23419999999999999</v>
+      </c>
+      <c r="C17" s="7">
+        <f t="shared" si="0"/>
+        <v>6.8317677198975232E-2</v>
+      </c>
+      <c r="D17" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>8</v>
+      </c>
+      <c r="B18" s="6">
+        <v>0.37709999999999999</v>
+      </c>
+      <c r="C18" s="7">
+        <f t="shared" si="0"/>
+        <v>4.2429063908777515E-2</v>
+      </c>
+      <c r="D18" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="12">
+        <v>8</v>
+      </c>
+      <c r="C34" s="12">
+        <v>2</v>
+      </c>
+      <c r="D34" s="7">
+        <f t="shared" ref="D34:D36" si="2">1/((1-$F$11)+$F$11/B34)</f>
+        <v>1</v>
+      </c>
+      <c r="E34" s="7">
+        <f t="shared" ref="E34:E36" si="3">D34*C34</f>
+        <v>2</v>
+      </c>
+      <c r="F34" s="9">
+        <f>ROUND(($E$34/E34)*MIN($B$11:$B$30),1)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="12">
+        <v>8</v>
+      </c>
+      <c r="C35" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="D35" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E35" s="7">
+        <f t="shared" si="3"/>
+        <v>3.2</v>
+      </c>
+      <c r="F35" s="9">
+        <f>ROUND(($E$34/E35)*MIN($B$11:$B$30),1)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" t="e">
+        <f t="shared" ref="G35:G36" si="4">ROUND(100*((F34-F35)/F34),2)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="12">
+        <v>12</v>
+      </c>
+      <c r="C36" s="12">
+        <v>2.6</v>
+      </c>
+      <c r="D36" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E36" s="7">
+        <f t="shared" si="3"/>
+        <v>2.6</v>
+      </c>
+      <c r="F36" s="9">
+        <f>ROUND(($E$34/E36)*MIN($B$11:$B$30),1)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C38" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4393376-7CF9-4231-9E85-0013D16FF48B}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>1</v>
+      </c>
+      <c r="B11" s="6">
+        <v>0.31819999999999998</v>
+      </c>
+      <c r="C11" s="7">
+        <f t="shared" ref="C11:C18" si="0">B$11/B11</f>
+        <v>1</v>
+      </c>
+      <c r="D11" s="7">
+        <f t="shared" ref="D11:D18" si="1">1/((1-F$11)+F$11/$A11)</f>
+        <v>1</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>2</v>
+      </c>
+      <c r="B12" s="6">
+        <v>0.20949999999999999</v>
+      </c>
+      <c r="C12" s="7">
+        <f t="shared" si="0"/>
+        <v>1.518854415274463</v>
+      </c>
+      <c r="D12" s="7">
+        <f t="shared" si="1"/>
+        <v>1.3986013986013985</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>3</v>
+      </c>
+      <c r="B13" s="6">
+        <v>0.20380000000000001</v>
+      </c>
+      <c r="C13" s="7">
+        <f t="shared" si="0"/>
+        <v>1.5613346418056917</v>
+      </c>
+      <c r="D13" s="7">
+        <f t="shared" si="1"/>
+        <v>1.6129032258064517</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>4</v>
+      </c>
+      <c r="B14" s="6">
+        <v>0.1857</v>
+      </c>
+      <c r="C14" s="7">
+        <f t="shared" si="0"/>
+        <v>1.7135164243403338</v>
+      </c>
+      <c r="D14" s="7">
+        <f t="shared" si="1"/>
+        <v>1.7467248908296944</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>5</v>
+      </c>
+      <c r="B15" s="6">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="C15" s="7">
+        <f t="shared" si="0"/>
+        <v>1.839306358381503</v>
+      </c>
+      <c r="D15" s="7">
+        <f t="shared" si="1"/>
+        <v>1.838235294117647</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>6</v>
+      </c>
+      <c r="B16" s="6">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="C16" s="7">
+        <f t="shared" si="0"/>
+        <v>1.8940476190476188</v>
+      </c>
+      <c r="D16" s="7">
+        <f t="shared" si="1"/>
+        <v>1.9047619047619047</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>7</v>
+      </c>
+      <c r="B17" s="6">
+        <v>0.1895</v>
+      </c>
+      <c r="C17" s="7">
+        <f t="shared" si="0"/>
+        <v>1.6791556728232189</v>
+      </c>
+      <c r="D17" s="7">
+        <f t="shared" si="1"/>
+        <v>1.9553072625698322</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>8</v>
+      </c>
+      <c r="B18" s="6">
+        <v>0.38040000000000002</v>
+      </c>
+      <c r="C18" s="7">
+        <f t="shared" si="0"/>
+        <v>0.83648790746582535</v>
+      </c>
+      <c r="D18" s="7">
+        <f t="shared" si="1"/>
+        <v>1.9950124688279298</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="14" t="s">
         <v>14</v>
       </c>
       <c r="B34" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C34" s="14">
-        <v>2.6</v>
-      </c>
-      <c r="D34" s="8">
+        <v>2</v>
+      </c>
+      <c r="D34" s="7">
         <f t="shared" ref="D34:D36" si="2">1/((1-$F$11)+$F$11/B34)</f>
-        <v>7.8740157480314945</v>
-      </c>
-      <c r="E34" s="8">
+        <v>1.9950124688279298</v>
+      </c>
+      <c r="E34" s="7">
         <f t="shared" ref="E34:E36" si="3">D34*C34</f>
-        <v>20.472440944881885</v>
-      </c>
-      <c r="F34" s="11">
+        <v>3.9900249376558596</v>
+      </c>
+      <c r="F34" s="9">
         <f t="shared" ref="F34:F36" si="4">ROUND(($E$34/E34)*MIN($B$11:$B$30),1)</f>
-        <v>85.3</v>
-      </c>
-      <c r="G34" s="12" t="s">
+        <v>0.2</v>
+      </c>
+      <c r="G34" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="14" t="s">
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B35" s="14">
+      <c r="B35" s="12">
         <v>8</v>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="12">
         <v>3.2</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="7">
         <f t="shared" si="2"/>
-        <v>6.6115702479338836</v>
-      </c>
-      <c r="E35" s="8">
+        <v>1.9950124688279298</v>
+      </c>
+      <c r="E35" s="7">
         <f t="shared" si="3"/>
-        <v>21.15702479338843</v>
-      </c>
-      <c r="F35" s="11">
+        <v>6.384039900249376</v>
+      </c>
+      <c r="F35" s="9">
         <f t="shared" si="4"/>
-        <v>82.5</v>
+        <v>0.1</v>
       </c>
       <c r="G35">
         <f t="shared" ref="G35:G36" si="5">ROUND(100*((F34-F35)/F34),2)</f>
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="14">
+      <c r="B36" s="12">
         <v>12</v>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="12">
         <v>2.6</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="7">
         <f t="shared" si="2"/>
-        <v>9.0225563909774422</v>
-      </c>
-      <c r="E36" s="8">
+        <v>2.0942408376963351</v>
+      </c>
+      <c r="E36" s="7">
         <f t="shared" si="3"/>
-        <v>23.458646616541351</v>
-      </c>
-      <c r="F36" s="11">
+        <v>5.4450261780104716</v>
+      </c>
+      <c r="F36" s="9">
         <f t="shared" si="4"/>
-        <v>74.400000000000006</v>
+        <v>0.1</v>
       </c>
       <c r="G36">
         <f t="shared" si="5"/>
-        <v>9.82</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C38" s="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C38" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87E1137-7B53-4241-9C55-9A26B24F09FE}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>1</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1.6171</v>
+      </c>
+      <c r="C11" s="7">
+        <f t="shared" ref="C11:C18" si="0">B$11/B11</f>
+        <v>1</v>
+      </c>
+      <c r="D11" s="7">
+        <f t="shared" ref="D11:D18" si="1">1/((1-F$11)+F$11/$A11)</f>
+        <v>1</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>2</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1.2410000000000001</v>
+      </c>
+      <c r="C12" s="7">
+        <f t="shared" si="0"/>
+        <v>1.3030620467365026</v>
+      </c>
+      <c r="D12" s="7">
+        <f t="shared" si="1"/>
+        <v>1.5384615384615383</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>3</v>
+      </c>
+      <c r="B13" s="6">
+        <v>0.77539999999999998</v>
+      </c>
+      <c r="C13" s="7">
+        <f t="shared" si="0"/>
+        <v>2.0855042558679391</v>
+      </c>
+      <c r="D13" s="7">
+        <f t="shared" si="1"/>
+        <v>1.875</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>4</v>
+      </c>
+      <c r="B14" s="6">
+        <v>0.75139999999999996</v>
+      </c>
+      <c r="C14" s="7">
+        <f t="shared" si="0"/>
+        <v>2.1521160500399255</v>
+      </c>
+      <c r="D14" s="7">
+        <f t="shared" si="1"/>
+        <v>2.1052631578947367</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>5</v>
+      </c>
+      <c r="B15" s="6">
+        <v>0.75229999999999997</v>
+      </c>
+      <c r="C15" s="7">
+        <f t="shared" si="0"/>
+        <v>2.149541406353848</v>
+      </c>
+      <c r="D15" s="7">
+        <f t="shared" si="1"/>
+        <v>2.2727272727272725</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>6</v>
+      </c>
+      <c r="B16" s="6">
+        <v>0.8569</v>
+      </c>
+      <c r="C16" s="7">
+        <f t="shared" si="0"/>
+        <v>1.887151359551873</v>
+      </c>
+      <c r="D16" s="7">
+        <f t="shared" si="1"/>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>7</v>
+      </c>
+      <c r="B17" s="6">
+        <v>1.2977000000000001</v>
+      </c>
+      <c r="C17" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2461277645064344</v>
+      </c>
+      <c r="D17" s="7">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>8</v>
+      </c>
+      <c r="B18" s="6">
+        <v>0.70309999999999995</v>
+      </c>
+      <c r="C18" s="7">
+        <f t="shared" si="0"/>
+        <v>2.2999573318162425</v>
+      </c>
+      <c r="D18" s="7">
+        <f t="shared" si="1"/>
+        <v>2.5806451612903221</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="14">
+        <v>8</v>
+      </c>
+      <c r="C34" s="14">
+        <v>2</v>
+      </c>
+      <c r="D34" s="7">
+        <f t="shared" ref="D34:D36" si="2">1/((1-$F$11)+$F$11/B34)</f>
+        <v>2.5806451612903221</v>
+      </c>
+      <c r="E34" s="7">
+        <f t="shared" ref="E34:E36" si="3">D34*C34</f>
+        <v>5.1612903225806441</v>
+      </c>
+      <c r="F34" s="9">
+        <f t="shared" ref="F34:F36" si="4">ROUND(($E$34/E34)*MIN($B$11:$B$30),1)</f>
+        <v>0.7</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="12">
+        <v>8</v>
+      </c>
+      <c r="C35" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="D35" s="7">
+        <f t="shared" si="2"/>
+        <v>2.5806451612903221</v>
+      </c>
+      <c r="E35" s="7">
+        <f t="shared" si="3"/>
+        <v>8.2580645161290303</v>
+      </c>
+      <c r="F35" s="9">
+        <f t="shared" si="4"/>
+        <v>0.4</v>
+      </c>
+      <c r="G35">
+        <f t="shared" ref="G35:G36" si="5">ROUND(100*((F34-F35)/F34),2)</f>
+        <v>42.86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="12">
+        <v>12</v>
+      </c>
+      <c r="C36" s="12">
+        <v>2.6</v>
+      </c>
+      <c r="D36" s="7">
+        <f t="shared" si="2"/>
+        <v>2.7906976744186043</v>
+      </c>
+      <c r="E36" s="7">
+        <f t="shared" si="3"/>
+        <v>7.2558139534883717</v>
+      </c>
+      <c r="F36" s="9">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="5"/>
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C38" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E300BC44-2F95-41D6-A7F7-7EC66DEA865A}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>1</v>
+      </c>
+      <c r="B11" s="6">
+        <v>20860.599999999999</v>
+      </c>
+      <c r="C11" s="7">
+        <f t="shared" ref="C11:C18" si="0">B$11/B11</f>
+        <v>1</v>
+      </c>
+      <c r="D11" s="7">
+        <f t="shared" ref="D11:D18" si="1">1/((1-F$11)+F$11/$A11)</f>
+        <v>1</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>2</v>
+      </c>
+      <c r="B12" s="6">
+        <v>14232.6</v>
+      </c>
+      <c r="C12" s="7">
+        <f t="shared" si="0"/>
+        <v>1.465691440776808</v>
+      </c>
+      <c r="D12" s="7">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372878</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>3</v>
+      </c>
+      <c r="B13" s="6">
+        <v>9674.1</v>
+      </c>
+      <c r="C13" s="7">
+        <f t="shared" si="0"/>
+        <v>2.1563349562233176</v>
+      </c>
+      <c r="D13" s="7">
+        <f t="shared" si="1"/>
+        <v>2.2058823529411762</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>4</v>
+      </c>
+      <c r="B14" s="6">
+        <v>7744.8</v>
+      </c>
+      <c r="C14" s="7">
+        <f t="shared" si="0"/>
+        <v>2.6934975725648176</v>
+      </c>
+      <c r="D14" s="7">
+        <f t="shared" si="1"/>
+        <v>2.5974025974025974</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>5</v>
+      </c>
+      <c r="B15" s="6">
+        <v>7204.4</v>
+      </c>
+      <c r="C15" s="7">
+        <f t="shared" si="0"/>
+        <v>2.8955360612958745</v>
+      </c>
+      <c r="D15" s="7">
+        <f t="shared" si="1"/>
+        <v>2.9069767441860463</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>6</v>
+      </c>
+      <c r="B16" s="6">
+        <v>7115.5</v>
+      </c>
+      <c r="C16" s="7">
+        <f t="shared" si="0"/>
+        <v>2.9317124587168855</v>
+      </c>
+      <c r="D16" s="7">
+        <f t="shared" si="1"/>
+        <v>3.1578947368421049</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>7</v>
+      </c>
+      <c r="B17" s="6">
+        <v>6970.9</v>
+      </c>
+      <c r="C17" s="7">
+        <f t="shared" si="0"/>
+        <v>2.992526072673543</v>
+      </c>
+      <c r="D17" s="7">
+        <f t="shared" si="1"/>
+        <v>3.3653846153846154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>8</v>
+      </c>
+      <c r="B18" s="6">
+        <v>6802.7</v>
+      </c>
+      <c r="C18" s="7">
+        <f t="shared" si="0"/>
+        <v>3.0665177062048889</v>
+      </c>
+      <c r="D18" s="7">
+        <f t="shared" si="1"/>
+        <v>3.5398230088495573</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="14">
+        <v>8</v>
+      </c>
+      <c r="C34" s="14">
+        <v>2</v>
+      </c>
+      <c r="D34" s="7">
+        <f t="shared" ref="D34:D36" si="2">1/((1-$F$11)+$F$11/B34)</f>
+        <v>3.5398230088495573</v>
+      </c>
+      <c r="E34" s="7">
+        <f t="shared" ref="E34:E36" si="3">D34*C34</f>
+        <v>7.0796460176991145</v>
+      </c>
+      <c r="F34" s="9">
+        <f t="shared" ref="F34:F36" si="4">ROUND(($E$34/E34)*MIN($B$11:$B$30),1)</f>
+        <v>6802.7</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="12">
+        <v>8</v>
+      </c>
+      <c r="C35" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="D35" s="7">
+        <f t="shared" si="2"/>
+        <v>3.5398230088495573</v>
+      </c>
+      <c r="E35" s="7">
+        <f t="shared" si="3"/>
+        <v>11.327433628318584</v>
+      </c>
+      <c r="F35" s="9">
+        <f t="shared" si="4"/>
+        <v>4251.7</v>
+      </c>
+      <c r="G35">
+        <f t="shared" ref="G35:G36" si="5">ROUND(100*((F34-F35)/F34),2)</f>
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="12">
+        <v>12</v>
+      </c>
+      <c r="C36" s="12">
+        <v>2.6</v>
+      </c>
+      <c r="D36" s="7">
+        <f t="shared" si="2"/>
+        <v>4.0268456375838921</v>
+      </c>
+      <c r="E36" s="7">
+        <f t="shared" si="3"/>
+        <v>10.469798657718121</v>
+      </c>
+      <c r="F36" s="9">
+        <f t="shared" si="4"/>
+        <v>4600</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="5"/>
+        <v>-8.19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C38" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>1</v>
+      </c>
+      <c r="B11" s="6">
+        <v>78161.600000000006</v>
+      </c>
+      <c r="C11" s="7">
+        <f t="shared" ref="C11:C18" si="0">B$11/B11</f>
+        <v>1</v>
+      </c>
+      <c r="D11" s="7">
+        <f t="shared" ref="D11:D18" si="1">1/((1-F$11)+F$11/$A11)</f>
+        <v>1</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0.85</v>
+      </c>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>2</v>
+      </c>
+      <c r="B12" s="6">
+        <v>47868.6</v>
+      </c>
+      <c r="C12" s="7">
+        <f t="shared" si="0"/>
+        <v>1.6328365567407446</v>
+      </c>
+      <c r="D12" s="7">
+        <f t="shared" si="1"/>
+        <v>1.7391304347826089</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>3</v>
+      </c>
+      <c r="B13" s="6">
+        <v>34204.800000000003</v>
+      </c>
+      <c r="C13" s="7">
+        <f t="shared" si="0"/>
+        <v>2.2851061839274021</v>
+      </c>
+      <c r="D13" s="7">
+        <f t="shared" si="1"/>
+        <v>2.3076923076923075</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>4</v>
+      </c>
+      <c r="B14" s="6">
+        <v>27097.1</v>
+      </c>
+      <c r="C14" s="7">
+        <f t="shared" si="0"/>
+        <v>2.8845005554099887</v>
+      </c>
+      <c r="D14" s="7">
+        <f t="shared" si="1"/>
+        <v>2.7586206896551722</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>5</v>
+      </c>
+      <c r="B15" s="6">
+        <v>26504.9</v>
+      </c>
+      <c r="C15" s="7">
+        <f t="shared" si="0"/>
+        <v>2.9489490622488672</v>
+      </c>
+      <c r="D15" s="7">
+        <f t="shared" si="1"/>
+        <v>3.125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>6</v>
+      </c>
+      <c r="B16" s="6">
+        <v>24652.400000000001</v>
+      </c>
+      <c r="C16" s="7">
+        <f t="shared" si="0"/>
+        <v>3.1705472895133942</v>
+      </c>
+      <c r="D16" s="7">
+        <f t="shared" si="1"/>
+        <v>3.4285714285714284</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>7</v>
+      </c>
+      <c r="B17" s="6">
+        <v>23885.9</v>
+      </c>
+      <c r="C17" s="7">
+        <f t="shared" si="0"/>
+        <v>3.2722903470248137</v>
+      </c>
+      <c r="D17" s="7">
+        <f t="shared" si="1"/>
+        <v>3.6842105263157889</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>8</v>
+      </c>
+      <c r="B18" s="6">
+        <v>24374.6</v>
+      </c>
+      <c r="C18" s="7">
+        <f t="shared" si="0"/>
+        <v>3.2066823660695976</v>
+      </c>
+      <c r="D18" s="7">
+        <f t="shared" si="1"/>
+        <v>3.9024390243902434</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="14">
+        <v>8</v>
+      </c>
+      <c r="C34" s="14">
+        <v>2</v>
+      </c>
+      <c r="D34" s="7">
+        <f t="shared" ref="D34:D36" si="2">1/((1-$F$11)+$F$11/B34)</f>
+        <v>3.9024390243902434</v>
+      </c>
+      <c r="E34" s="7">
+        <f t="shared" ref="E34:E36" si="3">D34*C34</f>
+        <v>7.8048780487804867</v>
+      </c>
+      <c r="F34" s="9">
+        <f t="shared" ref="F34:F36" si="4">ROUND(($E$34/E34)*MIN($B$11:$B$30),1)</f>
+        <v>23885.9</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="12">
+        <v>6</v>
+      </c>
+      <c r="C35" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="D35" s="7">
+        <f t="shared" si="2"/>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="E35" s="7">
+        <f t="shared" si="3"/>
+        <v>10.971428571428572</v>
+      </c>
+      <c r="F35" s="9">
+        <f t="shared" si="4"/>
+        <v>16992</v>
+      </c>
+      <c r="G35">
+        <f t="shared" ref="G35:G36" si="5">ROUND(100*((F34-F35)/F34),2)</f>
+        <v>28.86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="12">
+        <v>10</v>
+      </c>
+      <c r="C36" s="12">
+        <v>2.6</v>
+      </c>
+      <c r="D36" s="7">
+        <f t="shared" si="2"/>
+        <v>4.2553191489361701</v>
+      </c>
+      <c r="E36" s="7">
+        <f t="shared" si="3"/>
+        <v>11.063829787234043</v>
+      </c>
+      <c r="F36" s="9">
+        <f t="shared" si="4"/>
+        <v>16850.099999999999</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="5"/>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="17"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C38" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
